--- a/docs/xlsx/jobs-2026-08-14.xlsx
+++ b/docs/xlsx/jobs-2026-08-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="761">
   <si>
     <t>Title</t>
   </si>
@@ -778,6 +778,45 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-compliance-specialist-san-francisco-bay-area-california/2525380820</t>
   </si>
   <si>
+    <t>Accountant (Hybrid)</t>
+  </si>
+  <si>
+    <t>1199SEIU Funds</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 66400.00 - 83000.00/year</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfa6e835a3034b559ee0e65bf823effc-accountant-hybrid-1199seiu-funds-new-york</t>
+  </si>
+  <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>ica.fund</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e50ef18cb9b46dd80cd74250b8c9460-accounting-manager-icafund-oakland</t>
+  </si>
+  <si>
     <t>America Saves Program Manager</t>
   </si>
   <si>
@@ -793,24 +832,51 @@
     <t>USD 80000.00 - 80000.00/year</t>
   </si>
   <si>
-    <t>Financial Literacy Personal Finance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/719cbb4b90574b40af6f21562931aa03-america-saves-program-manager-consumer-federation-of-america-washington</t>
   </si>
   <si>
+    <t>APOYO AL COORDINADOR DE PROYECTO</t>
+  </si>
+  <si>
+    <t>Médicos Sin Fronteras en México AC</t>
+  </si>
+  <si>
+    <t>Juárez, Chihuahua, MX</t>
+  </si>
+  <si>
+    <t>MXN 32700.00 - 32700.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/831d959944394fe2921f2aa30a275209-apoyo-al-coordinador-de-proyecto-medicos-sin-fronteras-en-mexico-ac-juarez</t>
+  </si>
+  <si>
+    <t>Assistant Engagement Producer</t>
+  </si>
+  <si>
+    <t>Food &amp; Environment Reporting Network</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Media, Agriculture, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b24a6be96fc49e4ac994e9dbb503ce5-assistant-engagement-producer-food-environment-reporting-network-philadelphia</t>
+  </si>
+  <si>
     <t>Associate Director of Events</t>
   </si>
   <si>
     <t>Powered by Professionals</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 105000.00/year</t>
   </si>
   <si>
@@ -838,6 +904,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/c8bfdf4e3dfa40419180a2b33370cbc1-associate-director-of-visitor-experience-ticketing-spoleto-festival-usa-charleston</t>
   </si>
   <si>
+    <t>Associate, State Environmental Campaigns</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f919d27715b48baa975461d42fb2ead-associate-state-environmental-campaigns-environment-america-anchorage</t>
+  </si>
+  <si>
+    <t>Benefits &amp; Payroll Specialist</t>
+  </si>
+  <si>
+    <t>GLIDE</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a05929cf7afc4dc0a2ddab7e8cf61b5b-benefits-payroll-specialist-glide-san-francisco</t>
+  </si>
+  <si>
+    <t>Bilingual Customer Service Specialist (Remote, Part-Time – Flexible Schedule)</t>
+  </si>
+  <si>
+    <t>Lemontree</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 15.00 - 15.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f594695fd2294b56916b47fe8733620b-bilingual-customer-service-specialist-remote-part-time-flexible-schedule-lemontree-new-york</t>
+  </si>
+  <si>
     <t>Café Promotions Lead</t>
   </si>
   <si>
@@ -859,6 +979,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/8d85e77e83f64f82ac9ccb68440973f3-cafe-promotions-lead-autistry-studios-san-rafael</t>
   </si>
   <si>
+    <t>Campaign Associate</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e898004e2ac54e8994b0e220140d10b9-campaign-associate-environment-america-chicago</t>
+  </si>
+  <si>
     <t>Civil Practice Law Graduate, Housing Justice – Tenant Defense – Fall 2027</t>
   </si>
   <si>
@@ -874,27 +1006,105 @@
     <t>https://www.idealist.org/en/nonprofit-job/c95443e199994f9aae93b11ba40d350c-civil-practice-law-graduate-housing-justice-tenant-defense-fall-2027-the-legal-aid-society-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Classroom Facilitator</t>
+  </si>
+  <si>
+    <t>Project Success</t>
+  </si>
+  <si>
+    <t>Mankato, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b30654f56b39488391b2aed30fbb11aa-classroom-facilitator-project-success-mankato</t>
+  </si>
+  <si>
+    <t>College Access Program Manager</t>
+  </si>
+  <si>
+    <t>Minds Matter Boston</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a6ac63b891843638932619ee46ef7f4-college-access-program-manager-minds-matter-boston-boston</t>
+  </si>
+  <si>
+    <t>Conservation Advocate</t>
+  </si>
+  <si>
+    <t>Concord, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a4216953e55649ed801eb2ea21d1db9a-conservation-advocate-environment-america-concord</t>
+  </si>
+  <si>
+    <t>Conservation and Wildlife Advocate</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b12a7924fef4b0ea90f02d9a34650be-conservation-and-wildlife-advocate-environment-america-washington</t>
+  </si>
+  <si>
+    <t>Conservation Campaigner</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 40250.00 - 40250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94256d38092e4c48891b68af1da0909c-conservation-campaigner-environment-america-denver</t>
+  </si>
+  <si>
     <t>Consultant</t>
   </si>
   <si>
     <t>SmithBucklin</t>
   </si>
   <si>
-    <t>USD 80000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/4deb4292b01d409a966e2ba12e9c4766-consultant-smithbucklin-washington</t>
   </si>
   <si>
+    <t>Consumer Watchdog Campaign Associate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/702ba461cb544d69ad19bda23a952aa1-consumer-watchdog-campaign-associate-us-pirg-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/522d3f723c9b42889a079739efd64910-consumer-watchdog-campaign-associate-us-pirg-boston</t>
+  </si>
+  <si>
     <t>Contract Curriculum Writer – Robotics Education</t>
   </si>
   <si>
     <t>NYC FIRST</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 30000.00 - 30000.00/year</t>
   </si>
   <si>
@@ -904,6 +1114,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/febac0a511a2470289f63f93f879465c-contract-curriculum-writer-robotics-education-nyc-first-new-york</t>
   </si>
   <si>
+    <t>Contract Curriculum Writer , Robotics Education (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/febac0a511a2470289f63f93f879465c-contract-curriculum-writer-robotics-education-remote-nyc-first-new-york</t>
+  </si>
+  <si>
+    <t>CreativeMornings Chapter Community Manager</t>
+  </si>
+  <si>
+    <t>CreativeMornings</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b88d4d2692e14c429465557377af124e-creativemornings-chapter-community-manager-creativemornings-kings-county</t>
+  </si>
+  <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21c1047b84e54230ad3b9b37c8c62e8b-development-assistant-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Dar-us-Sakina</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62fbc9b79551443eabf74d9c767d4b19-development-director-dar-us-sakina-houston</t>
+  </si>
+  <si>
     <t>Digital Design &amp; Communications Specialist</t>
   </si>
   <si>
@@ -916,6 +1186,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/eea372fd3cff4d3ba194d20659ba3494-digital-design-communications-specialist-womens-league-for-conservative-judaism-wlcj-new-york</t>
   </si>
   <si>
+    <t>Director of Education and Engagement</t>
+  </si>
+  <si>
+    <t>Cain Center for the Arts</t>
+  </si>
+  <si>
+    <t>Cornelius, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99f4842cb6954259b5976ec42bb10ab5-director-of-education-and-engagement-cain-center-for-the-arts-cornelius</t>
+  </si>
+  <si>
+    <t>Director of High School Programs</t>
+  </si>
+  <si>
+    <t>Cambridge School Volunteers, Inc. (CSV)</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 61500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1457f8d41a66425b991d9f5a6d6e3863-director-of-high-school-programs-cambridge-school-volunteers-inc-csv-cambridge</t>
+  </si>
+  <si>
+    <t>Director of Workforce Development</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Job Workplace, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04d73925c6ab421d90fcf27f52fa17b0-director-of-workforce-development-glide-san-francisco</t>
+  </si>
+  <si>
+    <t>Director, Global Information Security</t>
+  </si>
+  <si>
+    <t>Americares</t>
+  </si>
+  <si>
+    <t>USD 137319.00 - 150900.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29d84d7d37be41d4b81acd084487a351-director-global-information-security-americares-stamford</t>
+  </si>
+  <si>
+    <t>Director, Social Media</t>
+  </si>
+  <si>
+    <t>UnidosUS</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 112900.00 - 125400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/795b902adb7e427688a120b4ed63a78b-director-social-media-unidosus-washington</t>
+  </si>
+  <si>
     <t>Education Program and Member Services Coordinator</t>
   </si>
   <si>
@@ -931,6 +1279,225 @@
     <t>https://www.idealist.org/en/nonprofit-job/94849e0d4d724c518e06c1b0ac32a63e-education-program-and-member-services-coordinator-american-association-for-justice-washington</t>
   </si>
   <si>
+    <t>Executive &amp; Operations Manager for LGBTQ+ Nonprofit</t>
+  </si>
+  <si>
+    <t>The Curve Foundation</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Lgbtq, Media, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24782491b59e4d27979a0978e2717188-executive-operations-manager-for-lgbtq-nonprofit-the-curve-foundation-oakland</t>
+  </si>
+  <si>
+    <t>Executive and Operations Manager</t>
+  </si>
+  <si>
+    <t>Pro-Democracy Campaign</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80a16d8b5194467ca8c75e50f2d00f77-executive-and-operations-manager-pro-democracy-campaign-foxborough</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>GreenLight Fund</t>
+  </si>
+  <si>
+    <t>Washington DC, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bc1bc92a72404d6b924d78659b820c69-executive-director-greenlight-fund-washington-dc</t>
+  </si>
+  <si>
+    <t>CENTER FOR COMMUNITY COUNSELING</t>
+  </si>
+  <si>
+    <t>Eugene, Oregon</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6de2baa39cba48b1a6fcb64ae6bc890e-executive-director-center-for-community-counseling-eugene</t>
+  </si>
+  <si>
+    <t>Facilitador/a Educativo/a en el valle de Toluca ( Presencial)</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Toluca de Lerdo, Estado de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 15000.00 - 15000.00/month</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c854493d9fb947128487f93c0919a003-facilitadora-educativoa-en-el-valle-de-toluca-presencial-educacion-para-compartir-mexico-toluca-de-lerdo</t>
+  </si>
+  <si>
+    <t>Fall 2026 Organizing Fellowship</t>
+  </si>
+  <si>
+    <t>Lead Locally</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4460a68bd4284c47a213642fec43faf7-fall-2026-organizing-fellowship-lead-locally-phoenix</t>
+  </si>
+  <si>
+    <t>Field Organizer for Colorado District 8 (Contractor)</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t>Indianapolis, Indiana</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Volunteering, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/caadc54c9a0e40aba442f89ace9b9d87-field-organizer-for-colorado-district-8-contractor-addition-indianapolis</t>
+  </si>
+  <si>
+    <t>Field Organizer for Wisconsin District 3 (Contractor)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50e8603bfadd4789816e7aa90f357a20-field-organizer-for-wisconsin-district-3-contractor-addition-indianapolis</t>
+  </si>
+  <si>
+    <t>Finance Administrator</t>
+  </si>
+  <si>
+    <t>Grace Church Brooklyn Heights</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12a0b24079f34ff2a774c293e583518e-finance-administrator-grace-church-brooklyn-heights-brooklyn</t>
+  </si>
+  <si>
+    <t>Finance Director (part-time)</t>
+  </si>
+  <si>
+    <t>Bellevue Botanical Garden Society</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15b07c9f958447db8a749e2ad33b35ae-finance-director-part-time-bellevue-botanical-garden-society-bellevue</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>League of Women Voters of NYS</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10e8f5102d2e47379d73e89c57d98835-finance-manager-league-of-women-voters-of-nys-albany</t>
+  </si>
+  <si>
+    <t>Grant and Revenue Accountant</t>
+  </si>
+  <si>
+    <t>Vision To Learn</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d71b92f479e84c5a9420c8a05721b1e4-grant-and-revenue-accountant-vision-to-learn-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ad58cc6edbd449e94ec373372480b01-grant-and-revenue-accountant-vision-to-learn-los-angeles</t>
+  </si>
+  <si>
+    <t>Grant Writer and Coordinator</t>
+  </si>
+  <si>
+    <t>MARIA DROSTE SERVICES OF COLORADO</t>
+  </si>
+  <si>
+    <t>Mental Health, Health Medicine, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1502c6ad222c4bc59aa90209c0baf4b2-grant-writer-and-coordinator-maria-droste-services-of-colorado-denver</t>
+  </si>
+  <si>
+    <t>Grants Officer</t>
+  </si>
+  <si>
+    <t>The Washington School for Girls</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/453f3d5a71dd469880c60cde8f9a5ba8-grants-officer-the-washington-school-for-girls-washington</t>
+  </si>
+  <si>
     <t>Graphic Designer</t>
   </si>
   <si>
@@ -949,6 +1516,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/ef3deb92b8b44566969f252e51e5a0bb-graphic-designer-alamo-heights-united-methodist-church-san-antonio</t>
   </si>
   <si>
+    <t>Healthcare Coordinator (Registered Nurse)</t>
+  </si>
+  <si>
+    <t>Cooperative for Human Services</t>
+  </si>
+  <si>
+    <t>Lexington, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 42.00 - 46.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcfdbe638df04f3bbbe045a4935be96f-healthcare-coordinator-registered-nurse-cooperative-for-human-services-lexington</t>
+  </si>
+  <si>
+    <t>Housing Program Manager</t>
+  </si>
+  <si>
+    <t>True Ground Housing Partners</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 79751.00 - 95700.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8af58cda39bb4ce49990cc249686df3f-housing-program-manager-true-ground-housing-partners-arlington</t>
+  </si>
+  <si>
     <t>HR Associate G6</t>
   </si>
   <si>
@@ -979,6 +1582,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f42e9499a45c4e0b81167135835b684e-human-resources-manager-heres-help-inc-miami-gardens</t>
   </si>
   <si>
+    <t>Internal Project Coordinator</t>
+  </si>
+  <si>
+    <t>Chihuly Studio</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 37.50 - 39.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/3993056c8107469ca1b95c48c9e0e17e-internal-project-coordinator-chihuly-studio-seattle</t>
+  </si>
+  <si>
     <t>IT Administrator</t>
   </si>
   <si>
@@ -1003,6 +1621,87 @@
     <t>https://www.idealist.org/en/nonprofit-job/81d3e0b0c29b41a18648fab0190772fe-juvenile-rights-practice-staff-attorney-entry-level-fall-2027-the-legal-aid-society-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Loan Portfolio Assistant</t>
+  </si>
+  <si>
+    <t>United Counties EDC</t>
+  </si>
+  <si>
+    <t>Cranford, NJ</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e48ade4632814ed98b33909ac6d268bb-loan-portfolio-assistant-united-counties-edc-cranford</t>
+  </si>
+  <si>
+    <t>Major Gift Officer</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>USD 89543.00 - 94256.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/042762baed5b4b31a1dd7f968c6b9cd1-major-gift-officer-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Riverdale Park, Maryland</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f86ba1a768ee44c8b9a1bc147adee4eb-major-gifts-officer-central-union-mission-riverdale-park</t>
+  </si>
+  <si>
+    <t>Manager of Media &amp; Content</t>
+  </si>
+  <si>
+    <t>Miami City Ballet</t>
+  </si>
+  <si>
+    <t>Miami Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e3c35bcbd8144eaba9f41a21dbccdec-manager-of-media-content-miami-city-ballet-miami-beach</t>
+  </si>
+  <si>
+    <t>Maritime Education Assistant Manager</t>
+  </si>
+  <si>
+    <t>Northwest Maritime</t>
+  </si>
+  <si>
+    <t>Burien, Washington</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/393623bd1a7b4faa87a405f87622f1e8-maritime-education-assistant-manager-northwest-maritime-burien</t>
+  </si>
+  <si>
     <t>Marketing and Communications Manager</t>
   </si>
   <si>
@@ -1021,15 +1720,81 @@
     <t>https://www.idealist.org/en/nonprofit-job/38b84c02f9a940eebdca3f35019a61a9-marketing-and-communications-manager-woodstock-farm-sanctuary-high-falls</t>
   </si>
   <si>
+    <t>Operations and Office Administrator</t>
+  </si>
+  <si>
+    <t>The Civic Federation</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/717de8141c164ab6b907b112b9020a03-operations-and-office-administrator-the-civic-federation-chicago</t>
+  </si>
+  <si>
+    <t>Oregon Campaign Associate</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/290408385c5e41e4889bf816b1ccf8da-oregon-campaign-associate-us-pirg-portland</t>
+  </si>
+  <si>
+    <t>PA Community Canvasser: work for a better PA</t>
+  </si>
+  <si>
+    <t>UNITE HERE Local 274</t>
+  </si>
+  <si>
+    <t>Pittston, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1fa456b64814a0393c0b09a414c4ab3-pa-community-canvasser-work-for-a-better-pa-unite-here-local-274-pittston</t>
+  </si>
+  <si>
+    <t>Bethlehem, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8194199fa60e4f84aa747148159faf4c-pa-community-canvasser-work-for-a-better-pa-unite-here-local-274-bethlehem</t>
+  </si>
+  <si>
+    <t>Part-Time Accountant</t>
+  </si>
+  <si>
+    <t>The Walden Woods Project</t>
+  </si>
+  <si>
+    <t>Lincoln, MA</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3076132e90584d019edc9396b2e89edd-part-time-accountant-the-walden-woods-project-lincoln</t>
+  </si>
+  <si>
     <t>Part-Time Communications Coordinator</t>
   </si>
   <si>
     <t>Mainline Protestant Stream - Powered by Faith</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 35.00 - 65.00/hour</t>
   </si>
   <si>
@@ -1039,15 +1804,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/faf16d3ee3614f73ba13a0cc9464f503-part-time-communications-coordinator-mainline-protestant-stream-powered-by-faith-san-jose</t>
   </si>
   <si>
+    <t>Part-Time Planned Giving &amp; Legacy Administrator</t>
+  </si>
+  <si>
+    <t>American Institute for Cancer Research</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1560371167b84c54a823e3faf3e7981a-part-time-planned-giving-legacy-administrator-american-institute-for-cancer-research-arlington</t>
+  </si>
+  <si>
     <t>Part-Time Programs Facilitator</t>
   </si>
   <si>
     <t>Pawsability Dog Club</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 20.00 - 22.00/hour</t>
   </si>
   <si>
@@ -1063,12 +1840,57 @@
     <t>Junior Achievement of New York</t>
   </si>
   <si>
-    <t>USD 25.00 - 25.00/hour</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e5925d8bf9a446c49a094245b557dc41-part-time-programs-manager-lower-hudson-valley-junior-achievement-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Payroll and Accounting Specialist</t>
+  </si>
+  <si>
+    <t>New York Civil Liberties Union Foundation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/faa0484ff96a4329aab7ac3970df44e7-payroll-and-accounting-specialist-new-york-civil-liberties-union-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Payroll Manager</t>
+  </si>
+  <si>
+    <t>Third Plateau Social Impact Strategies</t>
+  </si>
+  <si>
+    <t>USD 101000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/8ecfebb4c1f8475abb80576a3b135d2d-payroll-manager-third-plateau-social-impact-strategies-berkeley</t>
+  </si>
+  <si>
+    <t>Prevention Specialist Family Homelessness Prevention</t>
+  </si>
+  <si>
+    <t>Everyone Home DC</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96839f53aa8f412f8c5cf8cee36922f1-prevention-specialist-family-homelessness-prevention-everyone-home-dc-washington</t>
+  </si>
+  <si>
+    <t>Program and Data Assistant, Resident Services</t>
+  </si>
+  <si>
+    <t>USD 53768.00 - 64500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8801642a75844c469529500e01a5b75e-program-and-data-assistant-resident-services-true-ground-housing-partners-arlington</t>
+  </si>
+  <si>
     <t>PROGRAM COORDINATOR – WORKFORCE &amp; OPERATIONS</t>
   </si>
   <si>
@@ -1087,21 +1909,240 @@
     <t>https://www.idealist.org/en/nonprofit-job/79cdfd2b42964741a1b9bbe695060ff5-program-coordinator-workforce-operations-entryway-nc-raleigh</t>
   </si>
   <si>
+    <t>Programa Semilla: Acompañantes Comunitarios/as</t>
+  </si>
+  <si>
+    <t>Mennonite Central Committee</t>
+  </si>
+  <si>
+    <t>Sololá, Sololá Department, GT</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fd7287acb9c47e09bf994fd379c4fcb-programa-semilla-acompanantes-comunitariosas-mennonite-central-committee-solola</t>
+  </si>
+  <si>
+    <t>Programs &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>The Many Brains Project</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Science Technology, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50bdde0e7d83496cb9c778c36c04c81f-programs-operations-manager-the-many-brains-project-belmont</t>
+  </si>
+  <si>
+    <t>Programs &amp; Partnerships Manager</t>
+  </si>
+  <si>
+    <t>Old Pine Community Center</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a247bd0e0ba74cf9b8a59a9543e2e22c-programs-partnerships-manager-old-pine-community-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Receptionist/Admin Assistant</t>
+  </si>
+  <si>
+    <t>Institute for Contemporary Psychotherapy</t>
+  </si>
+  <si>
+    <t>USD 17.50/hour</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/742c5f717ae24e0696f292012c04fd42-receptionistadmin-assistant-institute-for-contemporary-psychotherapy-new-york</t>
+  </si>
+  <si>
+    <t>Rental Event Manager</t>
+  </si>
+  <si>
+    <t>Town Hall Seattle</t>
+  </si>
+  <si>
+    <t>USD 33.65 - 36.05/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be30ab50052f43568c0e34e21dc490ba-rental-event-manager-town-hall-seattle-seattle</t>
+  </si>
+  <si>
+    <t>Research Administrator</t>
+  </si>
+  <si>
+    <t>Public Policy Institute of California</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/954e066e72df4217b3d9fee35bd62e44-research-administrator-public-policy-institute-of-california-san-francisco</t>
+  </si>
+  <si>
+    <t>Scholar's Circle Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e3191ba374b4f6798fd750482bf5aba-scholars-circle-manager-the-washington-school-for-girls-washington</t>
+  </si>
+  <si>
     <t>Seasonal Program Facilitator</t>
   </si>
   <si>
     <t>Latinas On the Verge of Excellence - LOVE, Inc</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 21.00 - 21.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4e1e7eefd79d4e2b8ed35414435bffa7-seasonal-program-facilitator-latinas-on-the-verge-of-excellence-love-inc-new-york</t>
   </si>
   <si>
+    <t>Senior Associate, Community Planning</t>
+  </si>
+  <si>
+    <t>Jewish Federation of Cleveland</t>
+  </si>
+  <si>
+    <t>Beachwood, Ohio</t>
+  </si>
+  <si>
+    <t>Philanthropy, Volunteering, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c960cccbba974c0085e371f38c047217-senior-associate-community-planning-jewish-federation-of-cleveland-beachwood</t>
+  </si>
+  <si>
+    <t>Senior Director, Foundation Operations</t>
+  </si>
+  <si>
+    <t>U. S. Olympic &amp; Paralympic Committee</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e74102612114a4489cb6607ca953480-senior-director-foundation-operations-u-s-olympic-paralympic-committee-colorado-springs</t>
+  </si>
+  <si>
+    <t>Senior Director, Marketing and Strategic Communications</t>
+  </si>
+  <si>
+    <t>Pacific Institute</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecec048e6fbb45d8b7765ee0fb68892e-senior-director-marketing-and-strategic-communications-pacific-institute-oakland</t>
+  </si>
+  <si>
+    <t>Senior Director, Membership</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eaa731d1ed0c4cb1b191cfd8af9b2463-senior-director-membership-opb-portland</t>
+  </si>
+  <si>
+    <t>Senior Global Warming Campaign Director</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d46af460d9074f7587f0b8662e6ad080-senior-global-warming-campaign-director-environment-america-boston</t>
+  </si>
+  <si>
+    <t>Senior Manager, Payroll and Retirement Plan Administration</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>USD 126910.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88ce5955522a4824a2c2ef606b5e79ae-senior-manager-payroll-and-retirement-plan-administration-multiplier-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Program Associate (Salesforce-Focused)</t>
+  </si>
+  <si>
+    <t>Initiative for a Competitive Inner City (ICIC)</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3be17548f94d4898a9b9c30433f0135f-senior-program-associate-salesforce-focused-initiative-for-a-competitive-inner-city-icic-boston</t>
+  </si>
+  <si>
+    <t>Social Worker, Women's Defense Project and Mental Health Teams</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1a4fab7dd5b4c2894caa32d244e9db3-social-worker-womens-defense-project-and-mental-health-teams-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>USD 65600.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f486a35533f043449da21eeb95da8a43-staff-accountant-public-policy-institute-of-california-san-francisco</t>
+  </si>
+  <si>
     <t>Staff Attorney</t>
   </si>
   <si>
@@ -1111,15 +2152,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/b6da47718b5c4f599fe9d845b5a0bde3-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Staff Attorney - Farmworker Rights Project</t>
+  </si>
+  <si>
+    <t>Iowa Legal Aid</t>
+  </si>
+  <si>
+    <t>Des Moines, Iowa</t>
+  </si>
+  <si>
+    <t>USD 61800.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52e986f672004d15a1f528c30cf67799-staff-attorney-farmworker-rights-project-iowa-legal-aid-des-moines</t>
+  </si>
+  <si>
     <t>Staff Attorney, Child Advocacy Program</t>
   </si>
   <si>
     <t>Volunteer Legal Advocates</t>
   </si>
   <si>
-    <t>Washington, DC</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -1141,6 +2194,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d83b30f51a4549899af4378efa01602d-supervising-attorney-child-advocacy-program-volunteer-legal-advocates-washington</t>
   </si>
   <si>
+    <t>Survey outreach field staff - Palo Alto, California</t>
+  </si>
+  <si>
+    <t>ALTRANS Transportation Management</t>
+  </si>
+  <si>
+    <t>Palo Alto, California</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/113a38555a0d4850996f2b6a68199e26-survey-outreach-field-staff-palo-alto-california-altrans-transportation-management-palo-alto</t>
+  </si>
+  <si>
     <t>The Family Engagement &amp; Outreach Specialist</t>
   </si>
   <si>
@@ -1174,6 +2245,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/43a5a7ec6d62458ba230ea4c4ef1fcbe-vaga-de-preparadora-vocal-orquestra-e-coro-nova-sinfonia-agencia-do-bem-agencia-do-bem-rio-de-janeiro</t>
   </si>
   <si>
+    <t>Vice President, Civil and Human Rights</t>
+  </si>
+  <si>
+    <t>Lawyers for Good Government</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95337c7826de4921abe1f63774ce79b6-vice-president-civil-and-human-rights-lawyers-for-good-government-washington</t>
+  </si>
+  <si>
     <t>Vice President, Individual Giving</t>
   </si>
   <si>
@@ -1187,6 +2273,30 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3c1deb691b3d497aa40326c890de814b-vice-president-individual-giving-autism-speaks-as-new-york</t>
+  </si>
+  <si>
+    <t>Vice-President of Programs + Strategy</t>
+  </si>
+  <si>
+    <t>The Network: Advocating Against Domestic Violence</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6776e4bc01934e08942447341ae74702-vice-president-of-programs-strategy-the-network-advocating-against-domestic-violence-chicago</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>COMMUNITY SERVINGS INC</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/159e120fdef64446a42c33a2516c11cf-volunteer-coordinator-community-servings-inc-boston</t>
   </si>
 </sst>
 </file>
@@ -2774,7 +3884,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2847,105 +3957,105 @@
         <v>263</v>
       </c>
       <c r="D3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" t="s">
         <v>264</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>265</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" t="s">
         <v>268</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>269</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>270</v>
-      </c>
-      <c r="D4" t="s">
-        <v>264</v>
       </c>
       <c r="E4" t="s">
         <v>271</v>
       </c>
       <c r="F4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" t="s">
         <v>274</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>275</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5" t="s">
         <v>276</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>277</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="F5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" t="s">
         <v>281</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" t="s">
         <v>282</v>
       </c>
-      <c r="C6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>283</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" t="s">
         <v>286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>287</v>
       </c>
       <c r="C7" t="s">
         <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E7" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" t="s">
         <v>288</v>
-      </c>
-      <c r="F7" t="s">
-        <v>278</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>289</v>
@@ -2962,7 +4072,7 @@
         <v>292</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="E8" t="s">
         <v>293</v>
@@ -2982,433 +4092,2227 @@
         <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="D9" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C11" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="D11" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D12" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="F12" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B13" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="C13" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D13" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F13" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C14" t="s">
-        <v>323</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E14" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="F14" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="C15" t="s">
-        <v>263</v>
+        <v>332</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E15" t="s">
-        <v>283</v>
+        <v>333</v>
       </c>
       <c r="F15" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E16" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F16" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B17" t="s">
-        <v>336</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="D17" t="s">
-        <v>337</v>
+        <v>257</v>
       </c>
       <c r="E17" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F17" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" t="s">
-        <v>342</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
-        <v>343</v>
+        <v>269</v>
       </c>
       <c r="D18" t="s">
-        <v>337</v>
+        <v>257</v>
       </c>
       <c r="E18" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F18" t="s">
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B19" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>350</v>
       </c>
       <c r="D19" t="s">
-        <v>337</v>
+        <v>257</v>
       </c>
       <c r="E19" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F19" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C20" t="s">
-        <v>353</v>
+        <v>269</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E20" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="F20" t="s">
+        <v>318</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>356</v>
+      </c>
+      <c r="B21" t="s">
         <v>357</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E21" t="s">
+        <v>299</v>
+      </c>
+      <c r="F21" t="s">
         <v>358</v>
       </c>
-      <c r="C21" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="H21" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="E21" t="s">
-        <v>360</v>
-      </c>
-      <c r="F21" t="s">
-        <v>294</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B22" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="D22" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E22" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="F22" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>361</v>
+      </c>
+      <c r="B23" t="s">
+        <v>362</v>
+      </c>
+      <c r="C23" t="s">
+        <v>281</v>
+      </c>
+      <c r="D23" t="s">
+        <v>317</v>
+      </c>
+      <c r="E23" t="s">
+        <v>363</v>
+      </c>
+      <c r="F23" t="s">
+        <v>364</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="B23" t="s">
-        <v>366</v>
-      </c>
-      <c r="C23" t="s">
-        <v>367</v>
-      </c>
-      <c r="D23" t="s">
-        <v>264</v>
-      </c>
-      <c r="E23" t="s">
-        <v>368</v>
-      </c>
-      <c r="F23" t="s">
-        <v>369</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B24" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" t="s">
+        <v>317</v>
+      </c>
+      <c r="E24" t="s">
+        <v>363</v>
+      </c>
+      <c r="F24" t="s">
+        <v>364</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="D24" t="s">
-        <v>264</v>
-      </c>
-      <c r="E24" t="s">
-        <v>372</v>
-      </c>
-      <c r="F24" t="s">
-        <v>373</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B25" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C25" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D25" t="s">
-        <v>337</v>
+        <v>257</v>
       </c>
       <c r="E25" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="F25" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B26" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C26" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D26" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="E26" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F26" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>380</v>
+      </c>
+      <c r="B27" t="s">
+        <v>381</v>
+      </c>
+      <c r="C27" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" t="s">
+        <v>257</v>
+      </c>
+      <c r="E27" t="s">
+        <v>383</v>
+      </c>
+      <c r="F27" t="s">
+        <v>384</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>386</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>387</v>
       </c>
-      <c r="C27" t="s">
-        <v>292</v>
-      </c>
-      <c r="D27" t="s">
-        <v>264</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="C28" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28" t="s">
+        <v>257</v>
+      </c>
+      <c r="E28" t="s">
+        <v>305</v>
+      </c>
+      <c r="F28" t="s">
         <v>388</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H28" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="H27" s="2" t="s">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>390</v>
+      </c>
+      <c r="B29" t="s">
+        <v>391</v>
+      </c>
+      <c r="C29" t="s">
+        <v>392</v>
+      </c>
+      <c r="D29" t="s">
+        <v>257</v>
+      </c>
+      <c r="E29" t="s">
+        <v>393</v>
+      </c>
+      <c r="F29" t="s">
+        <v>394</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>396</v>
+      </c>
+      <c r="B30" t="s">
+        <v>397</v>
+      </c>
+      <c r="C30" t="s">
+        <v>398</v>
+      </c>
+      <c r="D30" t="s">
+        <v>257</v>
+      </c>
+      <c r="E30" t="s">
+        <v>399</v>
+      </c>
+      <c r="F30" t="s">
+        <v>400</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>402</v>
+      </c>
+      <c r="B31" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" t="s">
+        <v>304</v>
+      </c>
+      <c r="D31" t="s">
+        <v>257</v>
+      </c>
+      <c r="E31" t="s">
+        <v>403</v>
+      </c>
+      <c r="F31" t="s">
+        <v>404</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>406</v>
+      </c>
+      <c r="B32" t="s">
+        <v>407</v>
+      </c>
+      <c r="C32" t="s">
+        <v>281</v>
+      </c>
+      <c r="D32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E32" t="s">
+        <v>408</v>
+      </c>
+      <c r="F32" t="s">
+        <v>409</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>411</v>
+      </c>
+      <c r="B33" t="s">
+        <v>412</v>
+      </c>
+      <c r="C33" t="s">
+        <v>413</v>
+      </c>
+      <c r="D33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E33" t="s">
+        <v>414</v>
+      </c>
+      <c r="F33" t="s">
+        <v>318</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>416</v>
+      </c>
+      <c r="B34" t="s">
+        <v>417</v>
+      </c>
+      <c r="C34" t="s">
+        <v>269</v>
+      </c>
+      <c r="D34" t="s">
+        <v>257</v>
+      </c>
+      <c r="E34" t="s">
+        <v>418</v>
+      </c>
+      <c r="F34" t="s">
+        <v>419</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>421</v>
+      </c>
+      <c r="B35" t="s">
+        <v>422</v>
+      </c>
+      <c r="C35" t="s">
+        <v>281</v>
+      </c>
+      <c r="D35" t="s">
+        <v>310</v>
+      </c>
+      <c r="E35" t="s">
+        <v>423</v>
+      </c>
+      <c r="F35" t="s">
+        <v>424</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>426</v>
+      </c>
+      <c r="B36" t="s">
+        <v>427</v>
+      </c>
+      <c r="C36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" t="s">
+        <v>257</v>
+      </c>
+      <c r="E36" t="s">
+        <v>428</v>
+      </c>
+      <c r="F36" t="s">
+        <v>429</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>431</v>
+      </c>
+      <c r="B37" t="s">
+        <v>432</v>
+      </c>
+      <c r="C37" t="s">
+        <v>433</v>
+      </c>
+      <c r="D37" t="s">
+        <v>257</v>
+      </c>
+      <c r="E37" t="s">
+        <v>434</v>
+      </c>
+      <c r="F37" t="s">
+        <v>318</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>431</v>
+      </c>
+      <c r="B38" t="s">
+        <v>436</v>
+      </c>
+      <c r="C38" t="s">
+        <v>437</v>
+      </c>
+      <c r="D38" t="s">
+        <v>257</v>
+      </c>
+      <c r="E38" t="s">
+        <v>438</v>
+      </c>
+      <c r="F38" t="s">
+        <v>439</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>441</v>
+      </c>
+      <c r="B39" t="s">
+        <v>442</v>
+      </c>
+      <c r="C39" t="s">
+        <v>443</v>
+      </c>
+      <c r="D39" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" t="s">
+        <v>444</v>
+      </c>
+      <c r="F39" t="s">
+        <v>445</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>447</v>
+      </c>
+      <c r="B40" t="s">
+        <v>448</v>
+      </c>
+      <c r="C40" t="s">
+        <v>449</v>
+      </c>
+      <c r="D40" t="s">
+        <v>450</v>
+      </c>
+      <c r="E40" t="s">
+        <v>451</v>
+      </c>
+      <c r="F40" t="s">
+        <v>452</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>454</v>
+      </c>
+      <c r="B41" t="s">
+        <v>455</v>
+      </c>
+      <c r="C41" t="s">
+        <v>456</v>
+      </c>
+      <c r="D41" t="s">
+        <v>317</v>
+      </c>
+      <c r="E41" t="s">
+        <v>457</v>
+      </c>
+      <c r="F41" t="s">
+        <v>458</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>460</v>
+      </c>
+      <c r="B42" t="s">
+        <v>455</v>
+      </c>
+      <c r="C42" t="s">
+        <v>456</v>
+      </c>
+      <c r="D42" t="s">
+        <v>317</v>
+      </c>
+      <c r="E42" t="s">
+        <v>457</v>
+      </c>
+      <c r="F42" t="s">
+        <v>458</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>462</v>
+      </c>
+      <c r="B43" t="s">
+        <v>463</v>
+      </c>
+      <c r="C43" t="s">
+        <v>464</v>
+      </c>
+      <c r="D43" t="s">
+        <v>257</v>
+      </c>
+      <c r="E43" t="s">
+        <v>371</v>
+      </c>
+      <c r="F43" t="s">
+        <v>465</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>467</v>
+      </c>
+      <c r="B44" t="s">
+        <v>468</v>
+      </c>
+      <c r="C44" t="s">
+        <v>469</v>
+      </c>
+      <c r="D44" t="s">
+        <v>310</v>
+      </c>
+      <c r="E44" t="s">
+        <v>470</v>
+      </c>
+      <c r="F44" t="s">
+        <v>471</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>473</v>
+      </c>
+      <c r="B45" t="s">
+        <v>474</v>
+      </c>
+      <c r="C45" t="s">
+        <v>475</v>
+      </c>
+      <c r="D45" t="s">
+        <v>310</v>
+      </c>
+      <c r="E45" t="s">
+        <v>476</v>
+      </c>
+      <c r="F45" t="s">
+        <v>477</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>479</v>
+      </c>
+      <c r="B46" t="s">
+        <v>480</v>
+      </c>
+      <c r="C46" t="s">
+        <v>376</v>
+      </c>
+      <c r="D46" t="s">
+        <v>257</v>
+      </c>
+      <c r="E46" t="s">
+        <v>481</v>
+      </c>
+      <c r="F46" t="s">
+        <v>482</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>479</v>
+      </c>
+      <c r="B47" t="s">
+        <v>480</v>
+      </c>
+      <c r="C47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D47" t="s">
+        <v>257</v>
+      </c>
+      <c r="E47" t="s">
+        <v>481</v>
+      </c>
+      <c r="F47" t="s">
+        <v>482</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>485</v>
+      </c>
+      <c r="B48" t="s">
+        <v>486</v>
+      </c>
+      <c r="C48" t="s">
+        <v>350</v>
+      </c>
+      <c r="D48" t="s">
+        <v>310</v>
+      </c>
+      <c r="E48" t="s">
+        <v>476</v>
+      </c>
+      <c r="F48" t="s">
+        <v>487</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>489</v>
+      </c>
+      <c r="B49" t="s">
+        <v>490</v>
+      </c>
+      <c r="C49" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" t="s">
+        <v>257</v>
+      </c>
+      <c r="E49" t="s">
+        <v>491</v>
+      </c>
+      <c r="F49" t="s">
+        <v>492</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>494</v>
+      </c>
+      <c r="B50" t="s">
+        <v>495</v>
+      </c>
+      <c r="C50" t="s">
+        <v>496</v>
+      </c>
+      <c r="D50" t="s">
+        <v>257</v>
+      </c>
+      <c r="E50" t="s">
+        <v>497</v>
+      </c>
+      <c r="F50" t="s">
+        <v>498</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>500</v>
+      </c>
+      <c r="B51" t="s">
+        <v>501</v>
+      </c>
+      <c r="C51" t="s">
+        <v>502</v>
+      </c>
+      <c r="D51" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51" t="s">
+        <v>503</v>
+      </c>
+      <c r="F51" t="s">
+        <v>504</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>506</v>
+      </c>
+      <c r="B52" t="s">
+        <v>507</v>
+      </c>
+      <c r="C52" t="s">
+        <v>508</v>
+      </c>
+      <c r="D52" t="s">
+        <v>257</v>
+      </c>
+      <c r="E52" t="s">
+        <v>509</v>
+      </c>
+      <c r="F52" t="s">
+        <v>510</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>512</v>
+      </c>
+      <c r="B53" t="s">
+        <v>513</v>
+      </c>
+      <c r="C53" t="s">
+        <v>514</v>
+      </c>
+      <c r="D53" t="s">
+        <v>257</v>
+      </c>
+      <c r="E53" t="s">
+        <v>318</v>
+      </c>
+      <c r="F53" t="s">
+        <v>318</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>516</v>
+      </c>
+      <c r="B54" t="s">
+        <v>517</v>
+      </c>
+      <c r="C54" t="s">
+        <v>518</v>
+      </c>
+      <c r="D54" t="s">
+        <v>257</v>
+      </c>
+      <c r="E54" t="s">
+        <v>519</v>
+      </c>
+      <c r="F54" t="s">
+        <v>520</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>522</v>
+      </c>
+      <c r="B55" t="s">
+        <v>523</v>
+      </c>
+      <c r="C55" t="s">
+        <v>524</v>
+      </c>
+      <c r="D55" t="s">
+        <v>257</v>
+      </c>
+      <c r="E55" t="s">
+        <v>525</v>
+      </c>
+      <c r="F55" t="s">
+        <v>318</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>527</v>
+      </c>
+      <c r="B56" t="s">
+        <v>528</v>
+      </c>
+      <c r="C56" t="s">
+        <v>529</v>
+      </c>
+      <c r="D56" t="s">
+        <v>257</v>
+      </c>
+      <c r="E56" t="s">
+        <v>318</v>
+      </c>
+      <c r="F56" t="s">
+        <v>530</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>532</v>
+      </c>
+      <c r="B57" t="s">
+        <v>326</v>
+      </c>
+      <c r="C57" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57" t="s">
+        <v>257</v>
+      </c>
+      <c r="E57" t="s">
+        <v>327</v>
+      </c>
+      <c r="F57" t="s">
+        <v>533</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>535</v>
+      </c>
+      <c r="B58" t="s">
+        <v>536</v>
+      </c>
+      <c r="C58" t="s">
+        <v>537</v>
+      </c>
+      <c r="D58" t="s">
+        <v>257</v>
+      </c>
+      <c r="E58" t="s">
+        <v>538</v>
+      </c>
+      <c r="F58" t="s">
+        <v>539</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>541</v>
+      </c>
+      <c r="B59" t="s">
+        <v>542</v>
+      </c>
+      <c r="C59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" t="s">
+        <v>257</v>
+      </c>
+      <c r="E59" t="s">
+        <v>543</v>
+      </c>
+      <c r="F59" t="s">
+        <v>318</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>545</v>
+      </c>
+      <c r="B60" t="s">
+        <v>546</v>
+      </c>
+      <c r="C60" t="s">
+        <v>547</v>
+      </c>
+      <c r="D60" t="s">
+        <v>257</v>
+      </c>
+      <c r="E60" t="s">
+        <v>548</v>
+      </c>
+      <c r="F60" t="s">
+        <v>549</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>551</v>
+      </c>
+      <c r="B61" t="s">
+        <v>552</v>
+      </c>
+      <c r="C61" t="s">
+        <v>553</v>
+      </c>
+      <c r="D61" t="s">
+        <v>257</v>
+      </c>
+      <c r="E61" t="s">
+        <v>554</v>
+      </c>
+      <c r="F61" t="s">
+        <v>294</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>556</v>
+      </c>
+      <c r="B62" t="s">
+        <v>557</v>
+      </c>
+      <c r="C62" t="s">
+        <v>558</v>
+      </c>
+      <c r="D62" t="s">
+        <v>257</v>
+      </c>
+      <c r="E62" t="s">
+        <v>559</v>
+      </c>
+      <c r="F62" t="s">
+        <v>560</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>562</v>
+      </c>
+      <c r="B63" t="s">
+        <v>563</v>
+      </c>
+      <c r="C63" t="s">
+        <v>564</v>
+      </c>
+      <c r="D63" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" t="s">
+        <v>565</v>
+      </c>
+      <c r="F63" t="s">
+        <v>566</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>568</v>
+      </c>
+      <c r="B64" t="s">
+        <v>569</v>
+      </c>
+      <c r="C64" t="s">
+        <v>322</v>
+      </c>
+      <c r="D64" t="s">
+        <v>257</v>
+      </c>
+      <c r="E64" t="s">
+        <v>570</v>
+      </c>
+      <c r="F64" t="s">
+        <v>571</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>573</v>
+      </c>
+      <c r="B65" t="s">
+        <v>357</v>
+      </c>
+      <c r="C65" t="s">
+        <v>574</v>
+      </c>
+      <c r="D65" t="s">
+        <v>257</v>
+      </c>
+      <c r="E65" t="s">
+        <v>299</v>
+      </c>
+      <c r="F65" t="s">
+        <v>575</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>577</v>
+      </c>
+      <c r="B66" t="s">
+        <v>578</v>
+      </c>
+      <c r="C66" t="s">
+        <v>579</v>
+      </c>
+      <c r="D66" t="s">
+        <v>270</v>
+      </c>
+      <c r="E66" t="s">
+        <v>580</v>
+      </c>
+      <c r="F66" t="s">
+        <v>581</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>577</v>
+      </c>
+      <c r="B67" t="s">
+        <v>578</v>
+      </c>
+      <c r="C67" t="s">
+        <v>583</v>
+      </c>
+      <c r="D67" t="s">
+        <v>270</v>
+      </c>
+      <c r="E67" t="s">
+        <v>580</v>
+      </c>
+      <c r="F67" t="s">
+        <v>581</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>585</v>
+      </c>
+      <c r="B68" t="s">
+        <v>586</v>
+      </c>
+      <c r="C68" t="s">
+        <v>587</v>
+      </c>
+      <c r="D68" t="s">
+        <v>310</v>
+      </c>
+      <c r="E68" t="s">
+        <v>588</v>
+      </c>
+      <c r="F68" t="s">
+        <v>589</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>591</v>
+      </c>
+      <c r="B69" t="s">
+        <v>592</v>
+      </c>
+      <c r="C69" t="s">
+        <v>281</v>
+      </c>
+      <c r="D69" t="s">
+        <v>310</v>
+      </c>
+      <c r="E69" t="s">
+        <v>593</v>
+      </c>
+      <c r="F69" t="s">
+        <v>594</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>596</v>
+      </c>
+      <c r="B70" t="s">
+        <v>597</v>
+      </c>
+      <c r="C70" t="s">
+        <v>508</v>
+      </c>
+      <c r="D70" t="s">
+        <v>310</v>
+      </c>
+      <c r="E70" t="s">
+        <v>598</v>
+      </c>
+      <c r="F70" t="s">
+        <v>599</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>601</v>
+      </c>
+      <c r="B71" t="s">
+        <v>602</v>
+      </c>
+      <c r="C71" t="s">
+        <v>370</v>
+      </c>
+      <c r="D71" t="s">
+        <v>310</v>
+      </c>
+      <c r="E71" t="s">
+        <v>603</v>
+      </c>
+      <c r="F71" t="s">
+        <v>604</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>606</v>
+      </c>
+      <c r="B72" t="s">
+        <v>607</v>
+      </c>
+      <c r="C72" t="s">
+        <v>256</v>
+      </c>
+      <c r="D72" t="s">
+        <v>310</v>
+      </c>
+      <c r="E72" t="s">
+        <v>451</v>
+      </c>
+      <c r="F72" t="s">
+        <v>364</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>609</v>
+      </c>
+      <c r="B73" t="s">
+        <v>610</v>
+      </c>
+      <c r="C73" t="s">
+        <v>256</v>
+      </c>
+      <c r="D73" t="s">
+        <v>257</v>
+      </c>
+      <c r="E73" t="s">
+        <v>371</v>
+      </c>
+      <c r="F73" t="s">
+        <v>318</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>612</v>
+      </c>
+      <c r="B74" t="s">
+        <v>613</v>
+      </c>
+      <c r="C74" t="s">
+        <v>281</v>
+      </c>
+      <c r="D74" t="s">
+        <v>257</v>
+      </c>
+      <c r="E74" t="s">
+        <v>614</v>
+      </c>
+      <c r="F74" t="s">
+        <v>615</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>617</v>
+      </c>
+      <c r="B75" t="s">
+        <v>618</v>
+      </c>
+      <c r="C75" t="s">
+        <v>269</v>
+      </c>
+      <c r="D75" t="s">
+        <v>257</v>
+      </c>
+      <c r="E75" t="s">
+        <v>619</v>
+      </c>
+      <c r="F75" t="s">
+        <v>620</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>622</v>
+      </c>
+      <c r="B76" t="s">
+        <v>507</v>
+      </c>
+      <c r="C76" t="s">
+        <v>508</v>
+      </c>
+      <c r="D76" t="s">
+        <v>257</v>
+      </c>
+      <c r="E76" t="s">
+        <v>623</v>
+      </c>
+      <c r="F76" t="s">
+        <v>510</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>625</v>
+      </c>
+      <c r="B77" t="s">
+        <v>626</v>
+      </c>
+      <c r="C77" t="s">
+        <v>627</v>
+      </c>
+      <c r="D77" t="s">
+        <v>257</v>
+      </c>
+      <c r="E77" t="s">
+        <v>628</v>
+      </c>
+      <c r="F77" t="s">
+        <v>629</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>631</v>
+      </c>
+      <c r="B78" t="s">
+        <v>632</v>
+      </c>
+      <c r="C78" t="s">
+        <v>633</v>
+      </c>
+      <c r="D78" t="s">
+        <v>270</v>
+      </c>
+      <c r="E78" t="s">
+        <v>318</v>
+      </c>
+      <c r="F78" t="s">
+        <v>634</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>636</v>
+      </c>
+      <c r="B79" t="s">
+        <v>637</v>
+      </c>
+      <c r="C79" t="s">
+        <v>281</v>
+      </c>
+      <c r="D79" t="s">
+        <v>257</v>
+      </c>
+      <c r="E79" t="s">
+        <v>638</v>
+      </c>
+      <c r="F79" t="s">
+        <v>639</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>641</v>
+      </c>
+      <c r="B80" t="s">
+        <v>642</v>
+      </c>
+      <c r="C80" t="s">
+        <v>643</v>
+      </c>
+      <c r="D80" t="s">
+        <v>257</v>
+      </c>
+      <c r="E80" t="s">
+        <v>644</v>
+      </c>
+      <c r="F80" t="s">
+        <v>645</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>647</v>
+      </c>
+      <c r="B81" t="s">
+        <v>648</v>
+      </c>
+      <c r="C81" t="s">
+        <v>256</v>
+      </c>
+      <c r="D81" t="s">
+        <v>310</v>
+      </c>
+      <c r="E81" t="s">
+        <v>649</v>
+      </c>
+      <c r="F81" t="s">
+        <v>650</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>652</v>
+      </c>
+      <c r="B82" t="s">
+        <v>653</v>
+      </c>
+      <c r="C82" t="s">
+        <v>524</v>
+      </c>
+      <c r="D82" t="s">
+        <v>257</v>
+      </c>
+      <c r="E82" t="s">
+        <v>654</v>
+      </c>
+      <c r="F82" t="s">
+        <v>318</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>656</v>
+      </c>
+      <c r="B83" t="s">
+        <v>657</v>
+      </c>
+      <c r="C83" t="s">
+        <v>304</v>
+      </c>
+      <c r="D83" t="s">
+        <v>257</v>
+      </c>
+      <c r="E83" t="s">
+        <v>658</v>
+      </c>
+      <c r="F83" t="s">
+        <v>659</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>661</v>
+      </c>
+      <c r="B84" t="s">
+        <v>490</v>
+      </c>
+      <c r="C84" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" t="s">
+        <v>257</v>
+      </c>
+      <c r="E84" t="s">
+        <v>662</v>
+      </c>
+      <c r="F84" t="s">
+        <v>492</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>664</v>
+      </c>
+      <c r="B85" t="s">
+        <v>665</v>
+      </c>
+      <c r="C85" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85" t="s">
+        <v>450</v>
+      </c>
+      <c r="E85" t="s">
+        <v>666</v>
+      </c>
+      <c r="F85" t="s">
+        <v>364</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>668</v>
+      </c>
+      <c r="B86" t="s">
+        <v>669</v>
+      </c>
+      <c r="C86" t="s">
+        <v>670</v>
+      </c>
+      <c r="D86" t="s">
+        <v>257</v>
+      </c>
+      <c r="E86" t="s">
+        <v>318</v>
+      </c>
+      <c r="F86" t="s">
+        <v>671</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>673</v>
+      </c>
+      <c r="B87" t="s">
+        <v>674</v>
+      </c>
+      <c r="C87" t="s">
+        <v>281</v>
+      </c>
+      <c r="D87" t="s">
+        <v>257</v>
+      </c>
+      <c r="E87" t="s">
+        <v>675</v>
+      </c>
+      <c r="F87" t="s">
+        <v>676</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>678</v>
+      </c>
+      <c r="B88" t="s">
+        <v>679</v>
+      </c>
+      <c r="C88" t="s">
+        <v>281</v>
+      </c>
+      <c r="D88" t="s">
+        <v>257</v>
+      </c>
+      <c r="E88" t="s">
+        <v>680</v>
+      </c>
+      <c r="F88" t="s">
+        <v>300</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>682</v>
+      </c>
+      <c r="B89" t="s">
+        <v>683</v>
+      </c>
+      <c r="C89" t="s">
+        <v>75</v>
+      </c>
+      <c r="D89" t="s">
+        <v>257</v>
+      </c>
+      <c r="E89" t="s">
+        <v>684</v>
+      </c>
+      <c r="F89" t="s">
+        <v>685</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>687</v>
+      </c>
+      <c r="B90" t="s">
+        <v>297</v>
+      </c>
+      <c r="C90" t="s">
+        <v>338</v>
+      </c>
+      <c r="D90" t="s">
+        <v>257</v>
+      </c>
+      <c r="E90" t="s">
+        <v>688</v>
+      </c>
+      <c r="F90" t="s">
+        <v>689</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>691</v>
+      </c>
+      <c r="B91" t="s">
+        <v>692</v>
+      </c>
+      <c r="C91" t="s">
+        <v>281</v>
+      </c>
+      <c r="D91" t="s">
+        <v>257</v>
+      </c>
+      <c r="E91" t="s">
+        <v>693</v>
+      </c>
+      <c r="F91" t="s">
+        <v>694</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>696</v>
+      </c>
+      <c r="B92" t="s">
+        <v>697</v>
+      </c>
+      <c r="C92" t="s">
+        <v>281</v>
+      </c>
+      <c r="D92" t="s">
+        <v>257</v>
+      </c>
+      <c r="E92" t="s">
+        <v>698</v>
+      </c>
+      <c r="F92" t="s">
+        <v>699</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>701</v>
+      </c>
+      <c r="B93" t="s">
+        <v>702</v>
+      </c>
+      <c r="C93" t="s">
+        <v>464</v>
+      </c>
+      <c r="D93" t="s">
+        <v>257</v>
+      </c>
+      <c r="E93" t="s">
+        <v>703</v>
+      </c>
+      <c r="F93" t="s">
+        <v>704</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>706</v>
+      </c>
+      <c r="B94" t="s">
+        <v>657</v>
+      </c>
+      <c r="C94" t="s">
+        <v>304</v>
+      </c>
+      <c r="D94" t="s">
+        <v>257</v>
+      </c>
+      <c r="E94" t="s">
+        <v>707</v>
+      </c>
+      <c r="F94" t="s">
+        <v>659</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>709</v>
+      </c>
+      <c r="B95" t="s">
+        <v>710</v>
+      </c>
+      <c r="C95" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95" t="s">
+        <v>257</v>
+      </c>
+      <c r="E95" t="s">
+        <v>318</v>
+      </c>
+      <c r="F95" t="s">
+        <v>533</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>712</v>
+      </c>
+      <c r="B96" t="s">
+        <v>713</v>
+      </c>
+      <c r="C96" t="s">
+        <v>714</v>
+      </c>
+      <c r="D96" t="s">
+        <v>257</v>
+      </c>
+      <c r="E96" t="s">
+        <v>715</v>
+      </c>
+      <c r="F96" t="s">
+        <v>533</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>717</v>
+      </c>
+      <c r="B97" t="s">
+        <v>718</v>
+      </c>
+      <c r="C97" t="s">
+        <v>413</v>
+      </c>
+      <c r="D97" t="s">
+        <v>257</v>
+      </c>
+      <c r="E97" t="s">
+        <v>719</v>
+      </c>
+      <c r="F97" t="s">
+        <v>720</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>722</v>
+      </c>
+      <c r="B98" t="s">
+        <v>718</v>
+      </c>
+      <c r="C98" t="s">
+        <v>413</v>
+      </c>
+      <c r="D98" t="s">
+        <v>257</v>
+      </c>
+      <c r="E98" t="s">
+        <v>723</v>
+      </c>
+      <c r="F98" t="s">
+        <v>724</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>726</v>
+      </c>
+      <c r="B99" t="s">
+        <v>727</v>
+      </c>
+      <c r="C99" t="s">
+        <v>728</v>
+      </c>
+      <c r="D99" t="s">
+        <v>450</v>
+      </c>
+      <c r="E99" t="s">
+        <v>729</v>
+      </c>
+      <c r="F99" t="s">
+        <v>730</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>732</v>
+      </c>
+      <c r="B100" t="s">
+        <v>733</v>
+      </c>
+      <c r="C100" t="s">
+        <v>734</v>
+      </c>
+      <c r="D100" t="s">
+        <v>310</v>
+      </c>
+      <c r="E100" t="s">
+        <v>451</v>
+      </c>
+      <c r="F100" t="s">
+        <v>735</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>737</v>
+      </c>
+      <c r="B101" t="s">
+        <v>738</v>
+      </c>
+      <c r="C101" t="s">
+        <v>739</v>
+      </c>
+      <c r="D101" t="s">
+        <v>317</v>
+      </c>
+      <c r="E101" t="s">
+        <v>740</v>
+      </c>
+      <c r="F101" t="s">
+        <v>741</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>743</v>
+      </c>
+      <c r="B102" t="s">
+        <v>744</v>
+      </c>
+      <c r="C102" t="s">
+        <v>281</v>
+      </c>
+      <c r="D102" t="s">
+        <v>257</v>
+      </c>
+      <c r="E102" t="s">
+        <v>745</v>
+      </c>
+      <c r="F102" t="s">
+        <v>746</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>748</v>
+      </c>
+      <c r="B103" t="s">
+        <v>749</v>
+      </c>
+      <c r="C103" t="s">
+        <v>281</v>
+      </c>
+      <c r="D103" t="s">
+        <v>257</v>
+      </c>
+      <c r="E103" t="s">
+        <v>750</v>
+      </c>
+      <c r="F103" t="s">
+        <v>751</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>753</v>
+      </c>
+      <c r="B104" t="s">
+        <v>754</v>
+      </c>
+      <c r="C104" t="s">
+        <v>322</v>
+      </c>
+      <c r="D104" t="s">
+        <v>257</v>
+      </c>
+      <c r="E104" t="s">
+        <v>675</v>
+      </c>
+      <c r="F104" t="s">
+        <v>755</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>757</v>
+      </c>
+      <c r="B105" t="s">
+        <v>758</v>
+      </c>
+      <c r="C105" t="s">
+        <v>338</v>
+      </c>
+      <c r="D105" t="s">
+        <v>257</v>
+      </c>
+      <c r="E105" t="s">
+        <v>580</v>
+      </c>
+      <c r="F105" t="s">
+        <v>759</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -3440,6 +6344,84 @@
     <hyperlink ref="H25" r:id="rId24"/>
     <hyperlink ref="H26" r:id="rId25"/>
     <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-14.xlsx
+++ b/docs/xlsx/jobs-2026-08-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="766">
   <si>
     <t>Title</t>
   </si>
@@ -1262,6 +1262,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/795b902adb7e427688a120b4ed63a78b-director-social-media-unidosus-washington</t>
+  </si>
+  <si>
+    <t>Education &amp; Career Pathways Manager</t>
+  </si>
+  <si>
+    <t>A Place Called Home</t>
+  </si>
+  <si>
+    <t>USD 31.25 - 33.17/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcb69217b6a14554b61e0550c0970e04-education-career-pathways-manager-a-place-called-home-los-angeles</t>
   </si>
   <si>
     <t>Education Program and Member Services Coordinator</t>
@@ -3884,7 +3899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4667,7 +4682,7 @@
         <v>417</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>376</v>
       </c>
       <c r="D34" t="s">
         <v>257</v>
@@ -4690,10 +4705,10 @@
         <v>422</v>
       </c>
       <c r="C35" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D35" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="E35" t="s">
         <v>423</v>
@@ -4716,7 +4731,7 @@
         <v>281</v>
       </c>
       <c r="D36" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="E36" t="s">
         <v>428</v>
@@ -4736,16 +4751,16 @@
         <v>432</v>
       </c>
       <c r="C37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D37" t="s">
+        <v>257</v>
+      </c>
+      <c r="E37" t="s">
         <v>433</v>
       </c>
-      <c r="D37" t="s">
-        <v>257</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>434</v>
-      </c>
-      <c r="F37" t="s">
-        <v>318</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>435</v>
@@ -4753,22 +4768,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B38" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C38" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D38" t="s">
         <v>257</v>
       </c>
       <c r="E38" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F38" t="s">
-        <v>439</v>
+        <v>318</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>440</v>
@@ -4776,114 +4791,114 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>436</v>
+      </c>
+      <c r="B39" t="s">
         <v>441</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>442</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>257</v>
+      </c>
+      <c r="E39" t="s">
         <v>443</v>
       </c>
-      <c r="D39" t="s">
-        <v>270</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>444</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>446</v>
+      </c>
+      <c r="B40" t="s">
         <v>447</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>448</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>270</v>
+      </c>
+      <c r="E40" t="s">
         <v>449</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>450</v>
       </c>
-      <c r="E40" t="s">
+      <c r="H40" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="F40" t="s">
-        <v>452</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>452</v>
+      </c>
+      <c r="B41" t="s">
+        <v>453</v>
+      </c>
+      <c r="C41" t="s">
         <v>454</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>455</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>456</v>
       </c>
-      <c r="D41" t="s">
-        <v>317</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>457</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>459</v>
+      </c>
+      <c r="B42" t="s">
         <v>460</v>
       </c>
-      <c r="B42" t="s">
-        <v>455</v>
-      </c>
       <c r="C42" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D42" t="s">
         <v>317</v>
       </c>
       <c r="E42" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F42" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>465</v>
+      </c>
+      <c r="B43" t="s">
+        <v>460</v>
+      </c>
+      <c r="C43" t="s">
+        <v>461</v>
+      </c>
+      <c r="D43" t="s">
+        <v>317</v>
+      </c>
+      <c r="E43" t="s">
         <v>462</v>
       </c>
-      <c r="B43" t="s">
+      <c r="F43" t="s">
         <v>463</v>
-      </c>
-      <c r="C43" t="s">
-        <v>464</v>
-      </c>
-      <c r="D43" t="s">
-        <v>257</v>
-      </c>
-      <c r="E43" t="s">
-        <v>371</v>
-      </c>
-      <c r="F43" t="s">
-        <v>465</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>466</v>
@@ -4900,53 +4915,53 @@
         <v>469</v>
       </c>
       <c r="D44" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="E44" t="s">
+        <v>371</v>
+      </c>
+      <c r="F44" t="s">
         <v>470</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>472</v>
+      </c>
+      <c r="B45" t="s">
         <v>473</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>474</v>
-      </c>
-      <c r="C45" t="s">
-        <v>475</v>
       </c>
       <c r="D45" t="s">
         <v>310</v>
       </c>
       <c r="E45" t="s">
+        <v>475</v>
+      </c>
+      <c r="F45" t="s">
         <v>476</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>478</v>
+      </c>
+      <c r="B46" t="s">
         <v>479</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>480</v>
       </c>
-      <c r="C46" t="s">
-        <v>376</v>
-      </c>
       <c r="D46" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="E46" t="s">
         <v>481</v>
@@ -4960,65 +4975,65 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B47" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>376</v>
       </c>
       <c r="D47" t="s">
         <v>257</v>
       </c>
       <c r="E47" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F47" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>484</v>
+      </c>
+      <c r="B48" t="s">
         <v>485</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>281</v>
+      </c>
+      <c r="D48" t="s">
+        <v>257</v>
+      </c>
+      <c r="E48" t="s">
         <v>486</v>
-      </c>
-      <c r="C48" t="s">
-        <v>350</v>
-      </c>
-      <c r="D48" t="s">
-        <v>310</v>
-      </c>
-      <c r="E48" t="s">
-        <v>476</v>
       </c>
       <c r="F48" t="s">
         <v>487</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B49" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
       <c r="D49" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="E49" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="F49" t="s">
         <v>492</v>
@@ -5035,131 +5050,131 @@
         <v>495</v>
       </c>
       <c r="C50" t="s">
+        <v>269</v>
+      </c>
+      <c r="D50" t="s">
+        <v>257</v>
+      </c>
+      <c r="E50" t="s">
         <v>496</v>
       </c>
-      <c r="D50" t="s">
-        <v>257</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>497</v>
       </c>
-      <c r="F50" t="s">
+      <c r="H50" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>499</v>
+      </c>
+      <c r="B51" t="s">
         <v>500</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>501</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51" t="s">
         <v>502</v>
       </c>
-      <c r="D51" t="s">
-        <v>257</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>503</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>505</v>
+      </c>
+      <c r="B52" t="s">
         <v>506</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>507</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>257</v>
+      </c>
+      <c r="E52" t="s">
         <v>508</v>
       </c>
-      <c r="D52" t="s">
-        <v>257</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>509</v>
       </c>
-      <c r="F52" t="s">
+      <c r="H52" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>511</v>
+      </c>
+      <c r="B53" t="s">
         <v>512</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>513</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
+        <v>257</v>
+      </c>
+      <c r="E53" t="s">
         <v>514</v>
       </c>
-      <c r="D53" t="s">
-        <v>257</v>
-      </c>
-      <c r="E53" t="s">
-        <v>318</v>
-      </c>
       <c r="F53" t="s">
-        <v>318</v>
+        <v>515</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B54" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C54" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D54" t="s">
         <v>257</v>
       </c>
       <c r="E54" t="s">
-        <v>519</v>
+        <v>318</v>
       </c>
       <c r="F54" t="s">
+        <v>318</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>521</v>
+      </c>
+      <c r="B55" t="s">
         <v>522</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>523</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
+        <v>257</v>
+      </c>
+      <c r="E55" t="s">
         <v>524</v>
       </c>
-      <c r="D55" t="s">
-        <v>257</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>525</v>
-      </c>
-      <c r="F55" t="s">
-        <v>318</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>526</v>
@@ -5179,10 +5194,10 @@
         <v>257</v>
       </c>
       <c r="E56" t="s">
+        <v>530</v>
+      </c>
+      <c r="F56" t="s">
         <v>318</v>
-      </c>
-      <c r="F56" t="s">
-        <v>530</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>531</v>
@@ -5193,56 +5208,56 @@
         <v>532</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>533</v>
       </c>
       <c r="C57" t="s">
-        <v>256</v>
+        <v>534</v>
       </c>
       <c r="D57" t="s">
         <v>257</v>
       </c>
       <c r="E57" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="F57" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B58" t="s">
-        <v>536</v>
+        <v>326</v>
       </c>
       <c r="C58" t="s">
-        <v>537</v>
+        <v>256</v>
       </c>
       <c r="D58" t="s">
         <v>257</v>
       </c>
       <c r="E58" t="s">
+        <v>327</v>
+      </c>
+      <c r="F58" t="s">
         <v>538</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>540</v>
+      </c>
+      <c r="B59" t="s">
         <v>541</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>542</v>
-      </c>
-      <c r="C59" t="s">
-        <v>98</v>
       </c>
       <c r="D59" t="s">
         <v>257</v>
@@ -5251,21 +5266,21 @@
         <v>543</v>
       </c>
       <c r="F59" t="s">
-        <v>318</v>
+        <v>544</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C60" t="s">
-        <v>547</v>
+        <v>98</v>
       </c>
       <c r="D60" t="s">
         <v>257</v>
@@ -5274,30 +5289,30 @@
         <v>548</v>
       </c>
       <c r="F60" t="s">
+        <v>318</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>550</v>
+      </c>
+      <c r="B61" t="s">
         <v>551</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>552</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>257</v>
+      </c>
+      <c r="E61" t="s">
         <v>553</v>
       </c>
-      <c r="D61" t="s">
-        <v>257</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>554</v>
-      </c>
-      <c r="F61" t="s">
-        <v>294</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>555</v>
@@ -5320,44 +5335,44 @@
         <v>559</v>
       </c>
       <c r="F62" t="s">
+        <v>294</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>561</v>
+      </c>
+      <c r="B63" t="s">
         <v>562</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>563</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" t="s">
         <v>564</v>
       </c>
-      <c r="D63" t="s">
-        <v>257</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>565</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>567</v>
+      </c>
+      <c r="B64" t="s">
         <v>568</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>569</v>
-      </c>
-      <c r="C64" t="s">
-        <v>322</v>
       </c>
       <c r="D64" t="s">
         <v>257</v>
@@ -5377,102 +5392,102 @@
         <v>573</v>
       </c>
       <c r="B65" t="s">
-        <v>357</v>
+        <v>574</v>
       </c>
       <c r="C65" t="s">
-        <v>574</v>
+        <v>322</v>
       </c>
       <c r="D65" t="s">
         <v>257</v>
       </c>
       <c r="E65" t="s">
-        <v>299</v>
+        <v>575</v>
       </c>
       <c r="F65" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B66" t="s">
-        <v>578</v>
+        <v>357</v>
       </c>
       <c r="C66" t="s">
         <v>579</v>
       </c>
       <c r="D66" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="E66" t="s">
+        <v>299</v>
+      </c>
+      <c r="F66" t="s">
         <v>580</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B67" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C67" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D67" t="s">
         <v>270</v>
       </c>
       <c r="E67" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F67" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>582</v>
+      </c>
+      <c r="B68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C68" t="s">
+        <v>588</v>
+      </c>
+      <c r="D68" t="s">
+        <v>270</v>
+      </c>
+      <c r="E68" t="s">
         <v>585</v>
       </c>
-      <c r="B68" t="s">
+      <c r="F68" t="s">
         <v>586</v>
       </c>
-      <c r="C68" t="s">
-        <v>587</v>
-      </c>
-      <c r="D68" t="s">
-        <v>310</v>
-      </c>
-      <c r="E68" t="s">
-        <v>588</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="H68" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>590</v>
+      </c>
+      <c r="B69" t="s">
         <v>591</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>592</v>
-      </c>
-      <c r="C69" t="s">
-        <v>281</v>
       </c>
       <c r="D69" t="s">
         <v>310</v>
@@ -5495,7 +5510,7 @@
         <v>597</v>
       </c>
       <c r="C70" t="s">
-        <v>508</v>
+        <v>281</v>
       </c>
       <c r="D70" t="s">
         <v>310</v>
@@ -5518,7 +5533,7 @@
         <v>602</v>
       </c>
       <c r="C71" t="s">
-        <v>370</v>
+        <v>513</v>
       </c>
       <c r="D71" t="s">
         <v>310</v>
@@ -5541,62 +5556,62 @@
         <v>607</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>370</v>
       </c>
       <c r="D72" t="s">
         <v>310</v>
       </c>
       <c r="E72" t="s">
-        <v>451</v>
+        <v>608</v>
       </c>
       <c r="F72" t="s">
-        <v>364</v>
+        <v>609</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B73" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C73" t="s">
         <v>256</v>
       </c>
       <c r="D73" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="E73" t="s">
-        <v>371</v>
+        <v>456</v>
       </c>
       <c r="F73" t="s">
-        <v>318</v>
+        <v>364</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B74" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C74" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="D74" t="s">
         <v>257</v>
       </c>
       <c r="E74" t="s">
-        <v>614</v>
+        <v>371</v>
       </c>
       <c r="F74" t="s">
-        <v>615</v>
+        <v>318</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>616</v>
@@ -5610,7 +5625,7 @@
         <v>618</v>
       </c>
       <c r="C75" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D75" t="s">
         <v>257</v>
@@ -5630,33 +5645,33 @@
         <v>622</v>
       </c>
       <c r="B76" t="s">
-        <v>507</v>
+        <v>623</v>
       </c>
       <c r="C76" t="s">
-        <v>508</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
         <v>257</v>
       </c>
       <c r="E76" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F76" t="s">
-        <v>510</v>
+        <v>625</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B77" t="s">
-        <v>626</v>
+        <v>512</v>
       </c>
       <c r="C77" t="s">
-        <v>627</v>
+        <v>513</v>
       </c>
       <c r="D77" t="s">
         <v>257</v>
@@ -5665,27 +5680,27 @@
         <v>628</v>
       </c>
       <c r="F77" t="s">
+        <v>515</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>630</v>
+      </c>
+      <c r="B78" t="s">
         <v>631</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>632</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>257</v>
+      </c>
+      <c r="E78" t="s">
         <v>633</v>
-      </c>
-      <c r="D78" t="s">
-        <v>270</v>
-      </c>
-      <c r="E78" t="s">
-        <v>318</v>
       </c>
       <c r="F78" t="s">
         <v>634</v>
@@ -5702,13 +5717,13 @@
         <v>637</v>
       </c>
       <c r="C79" t="s">
-        <v>281</v>
+        <v>638</v>
       </c>
       <c r="D79" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="E79" t="s">
-        <v>638</v>
+        <v>318</v>
       </c>
       <c r="F79" t="s">
         <v>639</v>
@@ -5725,33 +5740,33 @@
         <v>642</v>
       </c>
       <c r="C80" t="s">
+        <v>281</v>
+      </c>
+      <c r="D80" t="s">
+        <v>257</v>
+      </c>
+      <c r="E80" t="s">
         <v>643</v>
       </c>
-      <c r="D80" t="s">
-        <v>257</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>644</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>646</v>
+      </c>
+      <c r="B81" t="s">
         <v>647</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>648</v>
       </c>
-      <c r="C81" t="s">
-        <v>256</v>
-      </c>
       <c r="D81" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="E81" t="s">
         <v>649</v>
@@ -5771,39 +5786,39 @@
         <v>653</v>
       </c>
       <c r="C82" t="s">
-        <v>524</v>
+        <v>256</v>
       </c>
       <c r="D82" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="E82" t="s">
         <v>654</v>
       </c>
       <c r="F82" t="s">
-        <v>318</v>
+        <v>655</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B83" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C83" t="s">
-        <v>304</v>
+        <v>529</v>
       </c>
       <c r="D83" t="s">
         <v>257</v>
       </c>
       <c r="E83" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F83" t="s">
-        <v>659</v>
+        <v>318</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>660</v>
@@ -5814,65 +5829,65 @@
         <v>661</v>
       </c>
       <c r="B84" t="s">
-        <v>490</v>
+        <v>662</v>
       </c>
       <c r="C84" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D84" t="s">
         <v>257</v>
       </c>
       <c r="E84" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F84" t="s">
-        <v>492</v>
+        <v>664</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B85" t="s">
-        <v>665</v>
+        <v>495</v>
       </c>
       <c r="C85" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>450</v>
+        <v>257</v>
       </c>
       <c r="E85" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F85" t="s">
-        <v>364</v>
+        <v>497</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B86" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C86" t="s">
-        <v>670</v>
+        <v>256</v>
       </c>
       <c r="D86" t="s">
-        <v>257</v>
+        <v>455</v>
       </c>
       <c r="E86" t="s">
-        <v>318</v>
+        <v>671</v>
       </c>
       <c r="F86" t="s">
-        <v>671</v>
+        <v>364</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>672</v>
@@ -5886,13 +5901,13 @@
         <v>674</v>
       </c>
       <c r="C87" t="s">
-        <v>281</v>
+        <v>675</v>
       </c>
       <c r="D87" t="s">
         <v>257</v>
       </c>
       <c r="E87" t="s">
-        <v>675</v>
+        <v>318</v>
       </c>
       <c r="F87" t="s">
         <v>676</v>
@@ -5918,30 +5933,30 @@
         <v>680</v>
       </c>
       <c r="F88" t="s">
-        <v>300</v>
+        <v>681</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B89" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C89" t="s">
-        <v>75</v>
+        <v>281</v>
       </c>
       <c r="D89" t="s">
         <v>257</v>
       </c>
       <c r="E89" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F89" t="s">
-        <v>685</v>
+        <v>300</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>686</v>
@@ -5952,33 +5967,33 @@
         <v>687</v>
       </c>
       <c r="B90" t="s">
-        <v>297</v>
+        <v>688</v>
       </c>
       <c r="C90" t="s">
-        <v>338</v>
+        <v>75</v>
       </c>
       <c r="D90" t="s">
         <v>257</v>
       </c>
       <c r="E90" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F90" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B91" t="s">
-        <v>692</v>
+        <v>297</v>
       </c>
       <c r="C91" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="D91" t="s">
         <v>257</v>
@@ -6024,7 +6039,7 @@
         <v>702</v>
       </c>
       <c r="C93" t="s">
-        <v>464</v>
+        <v>281</v>
       </c>
       <c r="D93" t="s">
         <v>257</v>
@@ -6044,65 +6059,65 @@
         <v>706</v>
       </c>
       <c r="B94" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="C94" t="s">
-        <v>304</v>
+        <v>469</v>
       </c>
       <c r="D94" t="s">
         <v>257</v>
       </c>
       <c r="E94" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F94" t="s">
-        <v>659</v>
+        <v>709</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B95" t="s">
-        <v>710</v>
+        <v>662</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="D95" t="s">
         <v>257</v>
       </c>
       <c r="E95" t="s">
-        <v>318</v>
+        <v>712</v>
       </c>
       <c r="F95" t="s">
-        <v>533</v>
+        <v>664</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B96" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C96" t="s">
-        <v>714</v>
+        <v>256</v>
       </c>
       <c r="D96" t="s">
         <v>257</v>
       </c>
       <c r="E96" t="s">
-        <v>715</v>
+        <v>318</v>
       </c>
       <c r="F96" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>716</v>
@@ -6116,16 +6131,16 @@
         <v>718</v>
       </c>
       <c r="C97" t="s">
-        <v>413</v>
+        <v>719</v>
       </c>
       <c r="D97" t="s">
         <v>257</v>
       </c>
       <c r="E97" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F97" t="s">
-        <v>720</v>
+        <v>538</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>721</v>
@@ -6136,7 +6151,7 @@
         <v>722</v>
       </c>
       <c r="B98" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="C98" t="s">
         <v>413</v>
@@ -6145,53 +6160,53 @@
         <v>257</v>
       </c>
       <c r="E98" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F98" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B99" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C99" t="s">
+        <v>413</v>
+      </c>
+      <c r="D99" t="s">
+        <v>257</v>
+      </c>
+      <c r="E99" t="s">
         <v>728</v>
       </c>
-      <c r="D99" t="s">
-        <v>450</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>729</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>731</v>
+      </c>
+      <c r="B100" t="s">
         <v>732</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>733</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
+        <v>455</v>
+      </c>
+      <c r="E100" t="s">
         <v>734</v>
-      </c>
-      <c r="D100" t="s">
-        <v>310</v>
-      </c>
-      <c r="E100" t="s">
-        <v>451</v>
       </c>
       <c r="F100" t="s">
         <v>735</v>
@@ -6211,30 +6226,30 @@
         <v>739</v>
       </c>
       <c r="D101" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E101" t="s">
+        <v>456</v>
+      </c>
+      <c r="F101" t="s">
         <v>740</v>
       </c>
-      <c r="F101" t="s">
+      <c r="H101" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>742</v>
+      </c>
+      <c r="B102" t="s">
         <v>743</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>744</v>
       </c>
-      <c r="C102" t="s">
-        <v>281</v>
-      </c>
       <c r="D102" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="E102" t="s">
         <v>745</v>
@@ -6277,42 +6292,65 @@
         <v>754</v>
       </c>
       <c r="C104" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="D104" t="s">
         <v>257</v>
       </c>
       <c r="E104" t="s">
-        <v>675</v>
+        <v>755</v>
       </c>
       <c r="F104" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B105" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C105" t="s">
+        <v>322</v>
+      </c>
+      <c r="D105" t="s">
+        <v>257</v>
+      </c>
+      <c r="E105" t="s">
+        <v>680</v>
+      </c>
+      <c r="F105" t="s">
+        <v>760</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>762</v>
+      </c>
+      <c r="B106" t="s">
+        <v>763</v>
+      </c>
+      <c r="C106" t="s">
         <v>338</v>
       </c>
-      <c r="D105" t="s">
-        <v>257</v>
-      </c>
-      <c r="E105" t="s">
-        <v>580</v>
-      </c>
-      <c r="F105" t="s">
-        <v>759</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>760</v>
+      <c r="D106" t="s">
+        <v>257</v>
+      </c>
+      <c r="E106" t="s">
+        <v>585</v>
+      </c>
+      <c r="F106" t="s">
+        <v>764</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -6422,6 +6460,7 @@
     <hyperlink ref="H103" r:id="rId102"/>
     <hyperlink ref="H104" r:id="rId103"/>
     <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
